--- a/paiement_mensuel_vto JUILLET.xlsx
+++ b/paiement_mensuel_vto JUILLET.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\Dossier LOUMA\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050"/>
   </bookViews>
   <sheets>
     <sheet name="DETAILS PAIEMENT JUILLET VTO" sheetId="1" r:id="rId1"/>
@@ -569,42 +569,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -615,6 +579,33 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -624,11 +615,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -941,7 +941,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34" style="48" customWidth="1"/>
+    <col min="2" max="2" width="34" style="33" customWidth="1"/>
     <col min="3" max="3" width="22.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.26953125" bestFit="1" customWidth="1"/>
@@ -962,35 +962,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="31"/>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="37" t="s">
+      <c r="A1" s="46"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
       <c r="K1" s="8"/>
-      <c r="L1" s="35" t="s">
+      <c r="L1" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
       <c r="Q1" s="15"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
     </row>
     <row r="2" spans="1:31" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1045,10 +1045,10 @@
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="41" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -1094,13 +1094,13 @@
       <c r="Q3" s="8"/>
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
-      <c r="AE3" s="32">
+      <c r="AE3" s="34">
         <v>150000</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A4" s="28"/>
-      <c r="B4" s="45"/>
+      <c r="A4" s="40"/>
+      <c r="B4" s="42"/>
       <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
@@ -1144,11 +1144,11 @@
       <c r="Q4" s="8"/>
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
-      <c r="AE4" s="33"/>
+      <c r="AE4" s="35"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A5" s="28"/>
-      <c r="B5" s="45"/>
+      <c r="A5" s="40"/>
+      <c r="B5" s="42"/>
       <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
@@ -1192,11 +1192,11 @@
       <c r="Q5" s="8"/>
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
-      <c r="AE5" s="33"/>
+      <c r="AE5" s="35"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A6" s="28"/>
-      <c r="B6" s="46"/>
+      <c r="A6" s="40"/>
+      <c r="B6" s="43"/>
       <c r="C6" s="2" t="s">
         <v>16</v>
       </c>
@@ -1240,13 +1240,13 @@
       <c r="Q6" s="8"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
-      <c r="AE6" s="34"/>
+      <c r="AE6" s="36"/>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="32" t="s">
         <v>61</v>
       </c>
       <c r="C7" s="20"/>
@@ -1279,10 +1279,10 @@
       <c r="AE7" s="2"/>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="44" t="s">
+      <c r="B8" s="41" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1328,15 +1328,15 @@
       <c r="Q8" s="8"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
-      <c r="AE8" s="32">
+      <c r="AE8" s="34">
         <v>150000</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="42" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -1382,13 +1382,13 @@
       <c r="Q9" s="8"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
-      <c r="AE9" s="33"/>
+      <c r="AE9" s="35"/>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="42" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1434,13 +1434,13 @@
       <c r="Q10" s="8"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
-      <c r="AE10" s="33"/>
+      <c r="AE10" s="35"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="43" t="s">
         <v>20</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1486,13 +1486,13 @@
       <c r="Q11" s="8"/>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
-      <c r="AE11" s="34"/>
+      <c r="AE11" s="36"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="47" t="s">
+      <c r="B12" s="32" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="20"/>
@@ -1525,10 +1525,10 @@
       <c r="AE12" s="2"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="41" t="s">
         <v>32</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -1574,15 +1574,15 @@
       <c r="Q13" s="8"/>
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
-      <c r="AE13" s="32">
+      <c r="AE13" s="34">
         <v>150000</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="42" t="s">
         <v>32</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -1628,13 +1628,13 @@
       <c r="Q14" s="8"/>
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
-      <c r="AE14" s="33"/>
+      <c r="AE14" s="35"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="42" t="s">
         <v>32</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -1680,13 +1680,13 @@
       <c r="Q15" s="8"/>
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
-      <c r="AE15" s="33"/>
+      <c r="AE15" s="35"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="43" t="s">
         <v>32</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -1732,13 +1732,13 @@
       <c r="Q16" s="8"/>
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
-      <c r="AE16" s="34"/>
+      <c r="AE16" s="36"/>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A17" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="47" t="s">
+      <c r="B17" s="32" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="20"/>
@@ -1771,10 +1771,10 @@
       <c r="AE17" s="2"/>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="44" t="s">
+      <c r="B18" s="41" t="s">
         <v>41</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -1820,15 +1820,15 @@
       <c r="Q18" s="8"/>
       <c r="R18" s="2"/>
       <c r="S18" s="2"/>
-      <c r="AE18" s="32">
+      <c r="AE18" s="34">
         <v>150000</v>
       </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="42" t="s">
         <v>41</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -1874,13 +1874,13 @@
       <c r="Q19" s="8"/>
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
-      <c r="AE19" s="33"/>
+      <c r="AE19" s="35"/>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="45" t="s">
+      <c r="B20" s="42" t="s">
         <v>41</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -1926,13 +1926,13 @@
       <c r="Q20" s="8"/>
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
-      <c r="AE20" s="33"/>
+      <c r="AE20" s="35"/>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="46" t="s">
+      <c r="B21" s="43" t="s">
         <v>41</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -1978,13 +1978,13 @@
       <c r="Q21" s="8"/>
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
-      <c r="AE21" s="34"/>
+      <c r="AE21" s="36"/>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A22" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="47" t="s">
+      <c r="B22" s="32" t="s">
         <v>18</v>
       </c>
       <c r="C22" s="20"/>
@@ -2017,10 +2017,10 @@
       <c r="AE22" s="2"/>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="44" t="s">
+      <c r="B23" s="41" t="s">
         <v>51</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -2066,15 +2066,15 @@
       <c r="Q23" s="8"/>
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
-      <c r="AE23" s="32">
+      <c r="AE23" s="34">
         <v>150000</v>
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A24" s="28" t="s">
+      <c r="A24" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="45" t="s">
+      <c r="B24" s="42" t="s">
         <v>51</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -2120,13 +2120,13 @@
       <c r="Q24" s="8"/>
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
-      <c r="AE24" s="33"/>
+      <c r="AE24" s="35"/>
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="45" t="s">
+      <c r="B25" s="42" t="s">
         <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -2172,13 +2172,13 @@
       <c r="Q25" s="8"/>
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
-      <c r="AE25" s="33"/>
+      <c r="AE25" s="35"/>
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="46" t="s">
+      <c r="B26" s="43" t="s">
         <v>51</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -2224,13 +2224,13 @@
       <c r="Q26" s="8"/>
       <c r="R26" s="2"/>
       <c r="S26" s="2"/>
-      <c r="AE26" s="34"/>
+      <c r="AE26" s="36"/>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A27" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B27" s="47" t="s">
+      <c r="B27" s="32" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="20"/>
@@ -2263,10 +2263,10 @@
       <c r="AE27" s="2"/>
     </row>
     <row r="28" spans="1:31" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="B28" s="44" t="s">
+      <c r="B28" s="41" t="s">
         <v>77</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -2314,10 +2314,10 @@
       <c r="S28" s="26"/>
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="45" t="s">
+      <c r="B29" s="42" t="s">
         <v>77</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -2365,10 +2365,10 @@
       <c r="S29" s="2"/>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="B30" s="45" t="s">
+      <c r="B30" s="42" t="s">
         <v>77</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -2416,10 +2416,10 @@
       <c r="S30" s="2"/>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="B31" s="46" t="s">
+      <c r="B31" s="43" t="s">
         <v>77</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -2470,7 +2470,7 @@
       <c r="A32" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B32" s="47" t="s">
+      <c r="B32" s="32" t="s">
         <v>18</v>
       </c>
       <c r="C32" s="20"/>
@@ -2503,47 +2503,38 @@
     </row>
     <row r="33" spans="11:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="K33" s="8"/>
-      <c r="L33" s="29" t="s">
+      <c r="L33" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="M33" s="29"/>
-      <c r="N33" s="29"/>
-      <c r="O33" s="29"/>
-      <c r="P33" s="29"/>
+      <c r="M33" s="44"/>
+      <c r="N33" s="44"/>
+      <c r="O33" s="44"/>
+      <c r="P33" s="44"/>
       <c r="Q33" s="8"/>
-      <c r="R33" s="29">
+      <c r="R33" s="44">
         <f>SUM(S3:S32)</f>
         <v>3588333</v>
       </c>
-      <c r="S33" s="29"/>
+      <c r="S33" s="44"/>
     </row>
     <row r="46" spans="11:19" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="L46" s="36" t="s">
+      <c r="L46" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="M46" s="36"/>
-      <c r="N46" s="36"/>
-      <c r="O46" s="36"/>
-      <c r="P46" s="36"/>
+      <c r="M46" s="38"/>
+      <c r="N46" s="38"/>
+      <c r="O46" s="38"/>
+      <c r="P46" s="38"/>
     </row>
     <row r="51" spans="18:19" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="R51" s="36">
+      <c r="R51" s="38">
         <f>SUM(S26:S49)</f>
         <v>1109167</v>
       </c>
-      <c r="S51" s="36"/>
+      <c r="S51" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="AE23:AE26"/>
-    <mergeCell ref="L1:P1"/>
-    <mergeCell ref="L46:P46"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="AE3:AE6"/>
-    <mergeCell ref="AE8:AE11"/>
-    <mergeCell ref="AE13:AE16"/>
-    <mergeCell ref="AE18:AE21"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="B28:B31"/>
     <mergeCell ref="L33:P33"/>
@@ -2560,6 +2551,15 @@
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="A13:A16"/>
+    <mergeCell ref="AE23:AE26"/>
+    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="L46:P46"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="AE3:AE6"/>
+    <mergeCell ref="AE8:AE11"/>
+    <mergeCell ref="AE13:AE16"/>
+    <mergeCell ref="AE18:AE21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2583,7 +2583,7 @@
       <c r="A1" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
@@ -2603,7 +2603,7 @@
       <c r="A2" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="30" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="24">
@@ -2625,7 +2625,7 @@
       <c r="A3" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="30" t="s">
         <v>20</v>
       </c>
       <c r="C3" s="24">
@@ -2647,7 +2647,7 @@
       <c r="A4" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="30" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="24">
@@ -2669,7 +2669,7 @@
       <c r="A5" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="30" t="s">
         <v>41</v>
       </c>
       <c r="C5" s="24">
@@ -2691,7 +2691,7 @@
       <c r="A6" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="30" t="s">
         <v>51</v>
       </c>
       <c r="C6" s="24">
@@ -2713,7 +2713,7 @@
       <c r="A7" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="31" t="s">
         <v>77</v>
       </c>
       <c r="C7" s="24">
@@ -2732,10 +2732,10 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="39"/>
+      <c r="C8" s="48"/>
       <c r="D8" s="21">
         <f>+D2+D3+D4+D5+D6</f>
         <v>3030833</v>
@@ -2750,7 +2750,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="E10" s="40"/>
+      <c r="E10" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/paiement_mensuel_vto JUILLET.xlsx
+++ b/paiement_mensuel_vto JUILLET.xlsx
@@ -585,6 +585,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -601,27 +622,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -962,29 +962,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="46"/>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="39" t="s">
+      <c r="A1" s="40"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
       <c r="K1" s="8"/>
-      <c r="L1" s="37" t="s">
+      <c r="L1" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
       <c r="Q1" s="15"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
     </row>
     <row r="2" spans="1:31" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
@@ -1045,10 +1045,10 @@
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="35" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -1094,13 +1094,13 @@
       <c r="Q3" s="8"/>
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
-      <c r="AE3" s="34">
+      <c r="AE3" s="41">
         <v>150000</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A4" s="40"/>
-      <c r="B4" s="42"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="36"/>
       <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
@@ -1144,11 +1144,11 @@
       <c r="Q4" s="8"/>
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
-      <c r="AE4" s="35"/>
+      <c r="AE4" s="42"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A5" s="40"/>
-      <c r="B5" s="42"/>
+      <c r="A5" s="34"/>
+      <c r="B5" s="36"/>
       <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
@@ -1192,11 +1192,11 @@
       <c r="Q5" s="8"/>
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
-      <c r="AE5" s="35"/>
+      <c r="AE5" s="42"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A6" s="40"/>
-      <c r="B6" s="43"/>
+      <c r="A6" s="34"/>
+      <c r="B6" s="37"/>
       <c r="C6" s="2" t="s">
         <v>16</v>
       </c>
@@ -1240,7 +1240,7 @@
       <c r="Q6" s="8"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
-      <c r="AE6" s="36"/>
+      <c r="AE6" s="43"/>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" s="19" t="s">
@@ -1279,10 +1279,10 @@
       <c r="AE7" s="2"/>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="35" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1328,15 +1328,15 @@
       <c r="Q8" s="8"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
-      <c r="AE8" s="34">
+      <c r="AE8" s="41">
         <v>150000</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="36" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -1382,13 +1382,13 @@
       <c r="Q9" s="8"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
-      <c r="AE9" s="35"/>
+      <c r="AE9" s="42"/>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="36" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1434,13 +1434,13 @@
       <c r="Q10" s="8"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
-      <c r="AE10" s="35"/>
+      <c r="AE10" s="42"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="37" t="s">
         <v>20</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1486,7 +1486,7 @@
       <c r="Q11" s="8"/>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
-      <c r="AE11" s="36"/>
+      <c r="AE11" s="43"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" s="19" t="s">
@@ -1525,10 +1525,10 @@
       <c r="AE12" s="2"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="35" t="s">
         <v>32</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -1574,15 +1574,15 @@
       <c r="Q13" s="8"/>
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
-      <c r="AE13" s="34">
+      <c r="AE13" s="41">
         <v>150000</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A14" s="40" t="s">
+      <c r="A14" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="42" t="s">
+      <c r="B14" s="36" t="s">
         <v>32</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -1628,13 +1628,13 @@
       <c r="Q14" s="8"/>
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
-      <c r="AE14" s="35"/>
+      <c r="AE14" s="42"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="36" t="s">
         <v>32</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -1680,13 +1680,13 @@
       <c r="Q15" s="8"/>
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
-      <c r="AE15" s="35"/>
+      <c r="AE15" s="42"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A16" s="40" t="s">
+      <c r="A16" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="37" t="s">
         <v>32</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -1732,7 +1732,7 @@
       <c r="Q16" s="8"/>
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
-      <c r="AE16" s="36"/>
+      <c r="AE16" s="43"/>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A17" s="19" t="s">
@@ -1771,10 +1771,10 @@
       <c r="AE17" s="2"/>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A18" s="40" t="s">
+      <c r="A18" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="35" t="s">
         <v>41</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -1820,15 +1820,15 @@
       <c r="Q18" s="8"/>
       <c r="R18" s="2"/>
       <c r="S18" s="2"/>
-      <c r="AE18" s="34">
+      <c r="AE18" s="41">
         <v>150000</v>
       </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A19" s="40" t="s">
+      <c r="A19" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="36" t="s">
         <v>41</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -1874,13 +1874,13 @@
       <c r="Q19" s="8"/>
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
-      <c r="AE19" s="35"/>
+      <c r="AE19" s="42"/>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="42" t="s">
+      <c r="B20" s="36" t="s">
         <v>41</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -1926,13 +1926,13 @@
       <c r="Q20" s="8"/>
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
-      <c r="AE20" s="35"/>
+      <c r="AE20" s="42"/>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A21" s="40" t="s">
+      <c r="A21" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="43" t="s">
+      <c r="B21" s="37" t="s">
         <v>41</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -1978,7 +1978,7 @@
       <c r="Q21" s="8"/>
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
-      <c r="AE21" s="36"/>
+      <c r="AE21" s="43"/>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A22" s="19" t="s">
@@ -2017,10 +2017,10 @@
       <c r="AE22" s="2"/>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A23" s="40" t="s">
+      <c r="A23" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="41" t="s">
+      <c r="B23" s="35" t="s">
         <v>51</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -2066,15 +2066,15 @@
       <c r="Q23" s="8"/>
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
-      <c r="AE23" s="34">
+      <c r="AE23" s="41">
         <v>150000</v>
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A24" s="40" t="s">
+      <c r="A24" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="36" t="s">
         <v>51</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -2120,13 +2120,13 @@
       <c r="Q24" s="8"/>
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
-      <c r="AE24" s="35"/>
+      <c r="AE24" s="42"/>
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A25" s="40" t="s">
+      <c r="A25" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="36" t="s">
         <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -2172,13 +2172,13 @@
       <c r="Q25" s="8"/>
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
-      <c r="AE25" s="35"/>
+      <c r="AE25" s="42"/>
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A26" s="40" t="s">
+      <c r="A26" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="43" t="s">
+      <c r="B26" s="37" t="s">
         <v>51</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -2224,7 +2224,7 @@
       <c r="Q26" s="8"/>
       <c r="R26" s="2"/>
       <c r="S26" s="2"/>
-      <c r="AE26" s="36"/>
+      <c r="AE26" s="43"/>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A27" s="19" t="s">
@@ -2263,10 +2263,10 @@
       <c r="AE27" s="2"/>
     </row>
     <row r="28" spans="1:31" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A28" s="40" t="s">
+      <c r="A28" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="B28" s="41" t="s">
+      <c r="B28" s="35" t="s">
         <v>77</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -2314,10 +2314,10 @@
       <c r="S28" s="26"/>
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A29" s="40" t="s">
+      <c r="A29" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="42" t="s">
+      <c r="B29" s="36" t="s">
         <v>77</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -2365,10 +2365,10 @@
       <c r="S29" s="2"/>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A30" s="40" t="s">
+      <c r="A30" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="B30" s="42" t="s">
+      <c r="B30" s="36" t="s">
         <v>77</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -2416,10 +2416,10 @@
       <c r="S30" s="2"/>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A31" s="40" t="s">
+      <c r="A31" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="B31" s="43" t="s">
+      <c r="B31" s="37" t="s">
         <v>77</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -2503,38 +2503,47 @@
     </row>
     <row r="33" spans="11:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="K33" s="8"/>
-      <c r="L33" s="44" t="s">
+      <c r="L33" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="M33" s="44"/>
-      <c r="N33" s="44"/>
-      <c r="O33" s="44"/>
-      <c r="P33" s="44"/>
+      <c r="M33" s="38"/>
+      <c r="N33" s="38"/>
+      <c r="O33" s="38"/>
+      <c r="P33" s="38"/>
       <c r="Q33" s="8"/>
-      <c r="R33" s="44">
+      <c r="R33" s="38">
         <f>SUM(S3:S32)</f>
         <v>3588333</v>
       </c>
-      <c r="S33" s="44"/>
+      <c r="S33" s="38"/>
     </row>
     <row r="46" spans="11:19" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="L46" s="38" t="s">
+      <c r="L46" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="M46" s="38"/>
-      <c r="N46" s="38"/>
-      <c r="O46" s="38"/>
-      <c r="P46" s="38"/>
+      <c r="M46" s="45"/>
+      <c r="N46" s="45"/>
+      <c r="O46" s="45"/>
+      <c r="P46" s="45"/>
     </row>
     <row r="51" spans="18:19" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="R51" s="38">
+      <c r="R51" s="45">
         <f>SUM(S26:S49)</f>
         <v>1109167</v>
       </c>
-      <c r="S51" s="38"/>
+      <c r="S51" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="AE23:AE26"/>
+    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="L46:P46"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="AE3:AE6"/>
+    <mergeCell ref="AE8:AE11"/>
+    <mergeCell ref="AE13:AE16"/>
+    <mergeCell ref="AE18:AE21"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="B28:B31"/>
     <mergeCell ref="L33:P33"/>
@@ -2551,15 +2560,6 @@
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="A13:A16"/>
-    <mergeCell ref="AE23:AE26"/>
-    <mergeCell ref="L1:P1"/>
-    <mergeCell ref="L46:P46"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="AE3:AE6"/>
-    <mergeCell ref="AE8:AE11"/>
-    <mergeCell ref="AE13:AE16"/>
-    <mergeCell ref="AE18:AE21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/paiement_mensuel_vto JUILLET.xlsx
+++ b/paiement_mensuel_vto JUILLET.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="DETAILS PAIEMENT JUILLET VTO" sheetId="1" r:id="rId1"/>
@@ -585,6 +585,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -604,24 +622,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -962,29 +962,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="40"/>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="46" t="s">
+      <c r="A1" s="46"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
       <c r="K1" s="8"/>
-      <c r="L1" s="44" t="s">
+      <c r="L1" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
       <c r="Q1" s="15"/>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
     </row>
     <row r="2" spans="1:31" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
@@ -1045,10 +1045,10 @@
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="41" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -1094,13 +1094,13 @@
       <c r="Q3" s="8"/>
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
-      <c r="AE3" s="41">
+      <c r="AE3" s="34">
         <v>150000</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A4" s="34"/>
-      <c r="B4" s="36"/>
+      <c r="A4" s="40"/>
+      <c r="B4" s="42"/>
       <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
@@ -1144,11 +1144,11 @@
       <c r="Q4" s="8"/>
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
-      <c r="AE4" s="42"/>
+      <c r="AE4" s="35"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A5" s="34"/>
-      <c r="B5" s="36"/>
+      <c r="A5" s="40"/>
+      <c r="B5" s="42"/>
       <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
@@ -1192,11 +1192,11 @@
       <c r="Q5" s="8"/>
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
-      <c r="AE5" s="42"/>
+      <c r="AE5" s="35"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A6" s="34"/>
-      <c r="B6" s="37"/>
+      <c r="A6" s="40"/>
+      <c r="B6" s="43"/>
       <c r="C6" s="2" t="s">
         <v>16</v>
       </c>
@@ -1240,7 +1240,7 @@
       <c r="Q6" s="8"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
-      <c r="AE6" s="43"/>
+      <c r="AE6" s="36"/>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" s="19" t="s">
@@ -1279,10 +1279,10 @@
       <c r="AE7" s="2"/>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="41" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1328,15 +1328,15 @@
       <c r="Q8" s="8"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
-      <c r="AE8" s="41">
+      <c r="AE8" s="34">
         <v>150000</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="42" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -1382,13 +1382,13 @@
       <c r="Q9" s="8"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
-      <c r="AE9" s="42"/>
+      <c r="AE9" s="35"/>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="42" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1434,13 +1434,13 @@
       <c r="Q10" s="8"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
-      <c r="AE10" s="42"/>
+      <c r="AE10" s="35"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="43" t="s">
         <v>20</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1486,7 +1486,7 @@
       <c r="Q11" s="8"/>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
-      <c r="AE11" s="43"/>
+      <c r="AE11" s="36"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" s="19" t="s">
@@ -1525,10 +1525,10 @@
       <c r="AE12" s="2"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A13" s="34" t="s">
+      <c r="A13" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="41" t="s">
         <v>32</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -1574,15 +1574,15 @@
       <c r="Q13" s="8"/>
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
-      <c r="AE13" s="41">
+      <c r="AE13" s="34">
         <v>150000</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="36" t="s">
+      <c r="B14" s="42" t="s">
         <v>32</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -1628,13 +1628,13 @@
       <c r="Q14" s="8"/>
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
-      <c r="AE14" s="42"/>
+      <c r="AE14" s="35"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="42" t="s">
         <v>32</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -1680,13 +1680,13 @@
       <c r="Q15" s="8"/>
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
-      <c r="AE15" s="42"/>
+      <c r="AE15" s="35"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="43" t="s">
         <v>32</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -1732,7 +1732,7 @@
       <c r="Q16" s="8"/>
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
-      <c r="AE16" s="43"/>
+      <c r="AE16" s="36"/>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A17" s="19" t="s">
@@ -1771,10 +1771,10 @@
       <c r="AE17" s="2"/>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A18" s="34" t="s">
+      <c r="A18" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="41" t="s">
         <v>41</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -1820,15 +1820,15 @@
       <c r="Q18" s="8"/>
       <c r="R18" s="2"/>
       <c r="S18" s="2"/>
-      <c r="AE18" s="41">
+      <c r="AE18" s="34">
         <v>150000</v>
       </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A19" s="34" t="s">
+      <c r="A19" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="42" t="s">
         <v>41</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -1874,13 +1874,13 @@
       <c r="Q19" s="8"/>
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
-      <c r="AE19" s="42"/>
+      <c r="AE19" s="35"/>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A20" s="34" t="s">
+      <c r="A20" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="42" t="s">
         <v>41</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -1926,13 +1926,13 @@
       <c r="Q20" s="8"/>
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
-      <c r="AE20" s="42"/>
+      <c r="AE20" s="35"/>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A21" s="34" t="s">
+      <c r="A21" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="37" t="s">
+      <c r="B21" s="43" t="s">
         <v>41</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -1978,7 +1978,7 @@
       <c r="Q21" s="8"/>
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
-      <c r="AE21" s="43"/>
+      <c r="AE21" s="36"/>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A22" s="19" t="s">
@@ -2017,10 +2017,10 @@
       <c r="AE22" s="2"/>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A23" s="34" t="s">
+      <c r="A23" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="35" t="s">
+      <c r="B23" s="41" t="s">
         <v>51</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -2066,15 +2066,15 @@
       <c r="Q23" s="8"/>
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
-      <c r="AE23" s="41">
+      <c r="AE23" s="34">
         <v>150000</v>
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A24" s="34" t="s">
+      <c r="A24" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="36" t="s">
+      <c r="B24" s="42" t="s">
         <v>51</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -2120,13 +2120,13 @@
       <c r="Q24" s="8"/>
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
-      <c r="AE24" s="42"/>
+      <c r="AE24" s="35"/>
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A25" s="34" t="s">
+      <c r="A25" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="36" t="s">
+      <c r="B25" s="42" t="s">
         <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -2172,13 +2172,13 @@
       <c r="Q25" s="8"/>
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
-      <c r="AE25" s="42"/>
+      <c r="AE25" s="35"/>
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A26" s="34" t="s">
+      <c r="A26" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="37" t="s">
+      <c r="B26" s="43" t="s">
         <v>51</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -2224,7 +2224,7 @@
       <c r="Q26" s="8"/>
       <c r="R26" s="2"/>
       <c r="S26" s="2"/>
-      <c r="AE26" s="43"/>
+      <c r="AE26" s="36"/>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A27" s="19" t="s">
@@ -2263,10 +2263,10 @@
       <c r="AE27" s="2"/>
     </row>
     <row r="28" spans="1:31" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="B28" s="35" t="s">
+      <c r="B28" s="41" t="s">
         <v>77</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -2314,10 +2314,10 @@
       <c r="S28" s="26"/>
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A29" s="34" t="s">
+      <c r="A29" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="36" t="s">
+      <c r="B29" s="42" t="s">
         <v>77</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -2365,10 +2365,10 @@
       <c r="S29" s="2"/>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A30" s="34" t="s">
+      <c r="A30" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="B30" s="36" t="s">
+      <c r="B30" s="42" t="s">
         <v>77</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -2416,10 +2416,10 @@
       <c r="S30" s="2"/>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A31" s="34" t="s">
+      <c r="A31" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="B31" s="37" t="s">
+      <c r="B31" s="43" t="s">
         <v>77</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -2503,47 +2503,38 @@
     </row>
     <row r="33" spans="11:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="K33" s="8"/>
-      <c r="L33" s="38" t="s">
+      <c r="L33" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="M33" s="38"/>
-      <c r="N33" s="38"/>
-      <c r="O33" s="38"/>
-      <c r="P33" s="38"/>
+      <c r="M33" s="44"/>
+      <c r="N33" s="44"/>
+      <c r="O33" s="44"/>
+      <c r="P33" s="44"/>
       <c r="Q33" s="8"/>
-      <c r="R33" s="38">
+      <c r="R33" s="44">
         <f>SUM(S3:S32)</f>
         <v>3588333</v>
       </c>
-      <c r="S33" s="38"/>
+      <c r="S33" s="44"/>
     </row>
     <row r="46" spans="11:19" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="L46" s="45" t="s">
+      <c r="L46" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="M46" s="45"/>
-      <c r="N46" s="45"/>
-      <c r="O46" s="45"/>
-      <c r="P46" s="45"/>
+      <c r="M46" s="38"/>
+      <c r="N46" s="38"/>
+      <c r="O46" s="38"/>
+      <c r="P46" s="38"/>
     </row>
     <row r="51" spans="18:19" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="R51" s="45">
+      <c r="R51" s="38">
         <f>SUM(S26:S49)</f>
         <v>1109167</v>
       </c>
-      <c r="S51" s="45"/>
+      <c r="S51" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="AE23:AE26"/>
-    <mergeCell ref="L1:P1"/>
-    <mergeCell ref="L46:P46"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="AE3:AE6"/>
-    <mergeCell ref="AE8:AE11"/>
-    <mergeCell ref="AE13:AE16"/>
-    <mergeCell ref="AE18:AE21"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="B28:B31"/>
     <mergeCell ref="L33:P33"/>
@@ -2560,6 +2551,15 @@
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="A13:A16"/>
+    <mergeCell ref="AE23:AE26"/>
+    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="L46:P46"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="AE3:AE6"/>
+    <mergeCell ref="AE8:AE11"/>
+    <mergeCell ref="AE13:AE16"/>
+    <mergeCell ref="AE18:AE21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
